--- a/public/downloads/AlonsoStrain2023.xlsx
+++ b/public/downloads/AlonsoStrain2023.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
@@ -659,10 +682,10 @@
         <v>2628</v>
       </c>
       <c r="N3" s="5">
-        <v>26032.96926736832</v>
+        <v>26032969.26736832</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03365454603523863</v>
+        <v>33.65454603523863</v>
       </c>
       <c r="P3" s="5">
         <v>773535</v>
@@ -709,10 +732,10 @@
         <v>2628</v>
       </c>
       <c r="N4" s="5">
-        <v>10199.12342691422</v>
+        <v>10199123.42691422</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03973029160221969</v>
+        <v>39.73029160221969</v>
       </c>
       <c r="P4" s="5">
         <v>256709</v>
@@ -759,10 +782,10 @@
         <v>2628</v>
       </c>
       <c r="N5" s="5">
-        <v>22966.77195239067</v>
+        <v>22966771.95239067</v>
       </c>
       <c r="O5" s="4">
-        <v>0.123858833677893</v>
+        <v>123.858833677893</v>
       </c>
       <c r="P5" s="5">
         <v>185427</v>
@@ -809,10 +832,10 @@
         <v>2628</v>
       </c>
       <c r="N6" s="5">
-        <v>23381.59402370453</v>
+        <v>23381594.02370453</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08914915269737692</v>
+        <v>89.14915269737692</v>
       </c>
       <c r="P6" s="5">
         <v>262275</v>
@@ -859,10 +882,10 @@
         <v>2628</v>
       </c>
       <c r="N7" s="5">
-        <v>72489.6767809391</v>
+        <v>72489676.7809391</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1460843354754142</v>
+        <v>146.0843354754142</v>
       </c>
       <c r="P7" s="5">
         <v>496218</v>
@@ -909,10 +932,10 @@
         <v>2628</v>
       </c>
       <c r="N8" s="5">
-        <v>4227.940214633942</v>
+        <v>4227940.214633942</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01075409507037811</v>
+        <v>10.75409507037811</v>
       </c>
       <c r="P8" s="5">
         <v>393147</v>
@@ -959,10 +982,10 @@
         <v>2628</v>
       </c>
       <c r="N9" s="5">
-        <v>8126.507363557816</v>
+        <v>8126507.363557816</v>
       </c>
       <c r="O9" s="4">
-        <v>0.0298160274570557</v>
+        <v>29.8160274570557</v>
       </c>
       <c r="P9" s="5">
         <v>272555</v>
@@ -1009,10 +1032,10 @@
         <v>2628</v>
       </c>
       <c r="N10" s="5">
-        <v>12744.14359974861</v>
+        <v>12744143.59974861</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08378792636258127</v>
+        <v>83.78792636258127</v>
       </c>
       <c r="P10" s="5">
         <v>152100</v>
@@ -1059,10 +1082,10 @@
         <v>2628</v>
       </c>
       <c r="N11" s="5">
-        <v>22593.64986181259</v>
+        <v>22593649.86181259</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0392749302705562</v>
+        <v>39.2749302705562</v>
       </c>
       <c r="P11" s="5">
         <v>575269</v>
@@ -1109,10 +1132,10 @@
         <v>2628</v>
       </c>
       <c r="N12" s="5">
-        <v>4103.689419269562</v>
+        <v>4103689.419269562</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01719384519034307</v>
+        <v>17.19384519034307</v>
       </c>
       <c r="P12" s="5">
         <v>238672</v>
@@ -1159,10 +1182,10 @@
         <v>2628</v>
       </c>
       <c r="N13" s="5">
-        <v>54055.67113518715</v>
+        <v>54055671.13518715</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07453065933781135</v>
+        <v>74.53065933781134</v>
       </c>
       <c r="P13" s="5">
         <v>725281</v>
@@ -1209,10 +1232,10 @@
         <v>2628</v>
       </c>
       <c r="N14" s="5">
-        <v>35163.77180409431</v>
+        <v>35163771.80409431</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2130840658822971</v>
+        <v>213.0840658822971</v>
       </c>
       <c r="P14" s="5">
         <v>165023</v>
@@ -1259,10 +1282,10 @@
         <v>2628</v>
       </c>
       <c r="N15" s="5">
-        <v>23932.0424258709</v>
+        <v>23932042.4258709</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2087527579169325</v>
+        <v>208.7527579169325</v>
       </c>
       <c r="P15" s="5">
         <v>114643</v>
@@ -1309,10 +1332,10 @@
         <v>2628</v>
       </c>
       <c r="N16" s="5">
-        <v>15794.68176436424</v>
+        <v>15794681.76436424</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09777264393428607</v>
+        <v>97.77264393428607</v>
       </c>
       <c r="P16" s="5">
         <v>161545</v>
@@ -1359,10 +1382,10 @@
         <v>2628</v>
       </c>
       <c r="N17" s="5">
-        <v>28048.05589914322</v>
+        <v>28048055.89914322</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09640660593996329</v>
+        <v>96.4066059399633</v>
       </c>
       <c r="P17" s="5">
         <v>290935</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1214963414706297</v>
+        <v>0.09286467622510093</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1076600661037158</v>
+        <v>0.08668988542441851</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1289136695863145</v>
+        <v>0.08859044858370471</v>
       </c>
       <c r="E3" s="4">
-        <v>88.79686502432702</v>
+        <v>93.9801422186997</v>
       </c>
       <c r="F3" s="4">
-        <v>91.82590879143949</v>
+        <v>95.63648583750157</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>863</v>
+        <v>906</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.003619283792173898</v>
+      </c>
+      <c r="O3" s="5">
+        <v>906</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09279800302524552</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08658571366901505</v>
+      </c>
+      <c r="R3" s="5">
+        <v>906</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5494107507370859</v>
+        <v>2.013630059449546</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5339052170328931</v>
+        <v>0.588218197755032</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5805850617897075</v>
+        <v>2.894651392712531</v>
       </c>
       <c r="E4" s="4">
-        <v>88.35123523093462</v>
+        <v>86.87010078387461</v>
       </c>
       <c r="F4" s="4">
-        <v>91.46365843210054</v>
+        <v>88.06726941586483</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>825</v>
+        <v>675</v>
       </c>
       <c r="I4" s="5">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J4" s="5">
+        <v>180</v>
+      </c>
+      <c r="K4" s="5">
+        <v>23</v>
+      </c>
+      <c r="L4" s="5">
+        <v>99</v>
+      </c>
+      <c r="M4" s="5">
+        <v>58</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.9375551521379093</v>
+      </c>
+      <c r="O4" s="5">
+        <v>733</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.651154583878645</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3719211319241655</v>
+      </c>
+      <c r="R4" s="5">
+        <v>685</v>
+      </c>
+      <c r="S4" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>51</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="B5" s="4">
-        <v>0.2644710074786991</v>
+        <v>1.284036689854188</v>
       </c>
       <c r="C5" s="4">
-        <v>0.161355659256877</v>
+        <v>0.1312646933949465</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2398321611574171</v>
+        <v>2.158448499100866</v>
       </c>
       <c r="E5" s="4">
-        <v>88.27469354078271</v>
+        <v>84.69290934195463</v>
       </c>
       <c r="F5" s="4">
-        <v>90.80971603871825</v>
+        <v>85.51722705827623</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>733</v>
+        <v>587</v>
       </c>
       <c r="I5" s="5">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="J5" s="5">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L5" s="5">
+        <v>79</v>
+      </c>
+      <c r="M5" s="5">
+        <v>48</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.3238937692369147</v>
+      </c>
+      <c r="O5" s="5">
+        <v>635</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.393499329906395</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3585449647558011</v>
+      </c>
+      <c r="R5" s="5">
+        <v>591</v>
+      </c>
+      <c r="S5" s="5">
         <v>44</v>
       </c>
-      <c r="M5" s="5">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2330156085753748</v>
+        <v>0.2679302675028883</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2125587598345318</v>
+        <v>0.249439555906455</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2091032177304294</v>
+        <v>0.2273639727727229</v>
       </c>
       <c r="E3" s="4">
-        <v>90.56069245389654</v>
+        <v>84.07282654161972</v>
       </c>
       <c r="F3" s="4">
-        <v>92.10766249405681</v>
+        <v>87.91230762919082</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="I3" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2044059334387915</v>
+      </c>
+      <c r="O3" s="5">
+        <v>851</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2016688685529673</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1903024239249593</v>
+      </c>
+      <c r="R3" s="5">
+        <v>851</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>4.257224398118683</v>
+        <v>1.502621592863205</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7327712653011308</v>
+        <v>0.8073037352511382</v>
       </c>
       <c r="D4" s="4">
-        <v>5.455726234447488</v>
+        <v>1.805827755950185</v>
       </c>
       <c r="E4" s="4">
-        <v>83.87671305924376</v>
+        <v>79.7658279437196</v>
       </c>
       <c r="F4" s="4">
-        <v>86.40602648990054</v>
+        <v>83.07333198052997</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>663</v>
+        <v>585</v>
       </c>
       <c r="I4" s="5">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="J4" s="5">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" s="5">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M4" s="5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>101</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.247397173131994</v>
+      </c>
+      <c r="O4" s="5">
+        <v>686</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.015137207472956</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5704116245415298</v>
+      </c>
+      <c r="R4" s="5">
+        <v>627</v>
+      </c>
+      <c r="S4" s="5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.897266500062457</v>
+        <v>0.7553044495602922</v>
       </c>
       <c r="C5" s="4">
-        <v>0.26008518593583</v>
+        <v>0.3922027002254465</v>
       </c>
       <c r="D5" s="4">
-        <v>4.226409282310253</v>
+        <v>1.015622506875911</v>
       </c>
       <c r="E5" s="4">
-        <v>81.35726072607267</v>
+        <v>76.81215060281531</v>
       </c>
       <c r="F5" s="4">
-        <v>83.5983011052784</v>
+        <v>79.610466919175</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>570</v>
+        <v>518</v>
       </c>
       <c r="I5" s="5">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="J5" s="5">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="K5" s="5">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="L5" s="5">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="M5" s="5">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.3666159674361618</v>
+      </c>
+      <c r="O5" s="5">
+        <v>550</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7283401058271604</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4019104994035934</v>
+      </c>
+      <c r="R5" s="5">
+        <v>519</v>
+      </c>
+      <c r="S5" s="5">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.09123191650480819</v>
+        <v>0.1214963414706297</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08417655533819021</v>
+        <v>0.1076600661037158</v>
       </c>
       <c r="D3" s="4">
-        <v>0.08855057052245559</v>
+        <v>0.1289136695863145</v>
       </c>
       <c r="E3" s="4">
-        <v>93.42634788543202</v>
+        <v>88.79686502432702</v>
       </c>
       <c r="F3" s="4">
-        <v>95.08392278379776</v>
+        <v>91.82590879143949</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>902</v>
+        <v>863</v>
       </c>
       <c r="I3" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.06758711403143478</v>
+      </c>
+      <c r="O3" s="5">
+        <v>863</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1070681769080011</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09375849520376456</v>
+      </c>
+      <c r="R3" s="5">
+        <v>863</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.718564590920399</v>
+        <v>0.5494107507370859</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6647650269659953</v>
+        <v>0.5339052170328931</v>
       </c>
       <c r="D4" s="4">
-        <v>3.204001034642507</v>
+        <v>0.5805850617897075</v>
       </c>
       <c r="E4" s="4">
-        <v>89.4854918451145</v>
+        <v>88.35123523093462</v>
       </c>
       <c r="F4" s="4">
-        <v>90.86120985742976</v>
+        <v>91.46365843210054</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>661</v>
+        <v>825</v>
       </c>
       <c r="I4" s="5">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="K4" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="M4" s="5">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.5288203692683235</v>
+      </c>
+      <c r="O4" s="5">
+        <v>825</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1820652230963759</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1575525373591131</v>
+      </c>
+      <c r="R4" s="5">
+        <v>825</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>2.014971371183639</v>
+        <v>0.2644710074786991</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1203553717364785</v>
+        <v>0.161355659256877</v>
       </c>
       <c r="D5" s="4">
-        <v>2.510899591506712</v>
+        <v>0.2398321611574171</v>
       </c>
       <c r="E5" s="4">
-        <v>86.3714891897352</v>
+        <v>88.27469354078271</v>
       </c>
       <c r="F5" s="4">
-        <v>87.00770538463219</v>
+        <v>90.80971603871825</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>565</v>
+        <v>733</v>
       </c>
       <c r="I5" s="5">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="K5" s="5">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="M5" s="5">
-        <v>94</v>
+        <v>7</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.04447902433617364</v>
+      </c>
+      <c r="O5" s="5">
+        <v>740</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2777432615016237</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1765125731106132</v>
+      </c>
+      <c r="R5" s="5">
+        <v>733</v>
+      </c>
+      <c r="S5" s="5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1607591438398197</v>
+        <v>0.2330156085753748</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1562897876752814</v>
+        <v>0.2125587598345318</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1527518511424315</v>
+        <v>0.2091032177304294</v>
       </c>
       <c r="E3" s="4">
-        <v>94.76550059074323</v>
+        <v>90.56069245389654</v>
       </c>
       <c r="F3" s="4">
-        <v>96.0178850251839</v>
+        <v>92.10766249405681</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>912</v>
+        <v>874</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.09461727144166959</v>
+      </c>
+      <c r="O3" s="5">
+        <v>874</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2151007541900198</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1987831788120364</v>
+      </c>
+      <c r="R3" s="5">
+        <v>874</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>3.112049723489646</v>
+        <v>4.257224398118683</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5567502838159225</v>
+        <v>0.7327712653011308</v>
       </c>
       <c r="D4" s="4">
-        <v>4.09725202065845</v>
+        <v>5.455726234447488</v>
       </c>
       <c r="E4" s="4">
-        <v>87.1514652893632</v>
+        <v>83.87671305924376</v>
       </c>
       <c r="F4" s="4">
-        <v>88.212294981349</v>
+        <v>86.40602648990054</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="I4" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4" s="5">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K4" s="5">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L4" s="5">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="M4" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>21</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.013791610127357</v>
+      </c>
+      <c r="O4" s="5">
+        <v>684</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.799907251233735</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4048345501024522</v>
+      </c>
+      <c r="R4" s="5">
+        <v>664</v>
+      </c>
+      <c r="S4" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.762780696314527</v>
+        <v>2.897266500062457</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2036587347705409</v>
+        <v>0.26008518593583</v>
       </c>
       <c r="D5" s="4">
-        <v>3.361708231014246</v>
+        <v>4.226409282310253</v>
       </c>
       <c r="E5" s="4">
-        <v>83.5375412541254</v>
+        <v>81.35726072607267</v>
       </c>
       <c r="F5" s="4">
-        <v>84.57176002835203</v>
+        <v>83.5983011052784</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="I5" s="5">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J5" s="5">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="K5" s="5">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L5" s="5">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M5" s="5">
-        <v>14</v>
+        <v>34</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.9292749066123122</v>
+      </c>
+      <c r="O5" s="5">
+        <v>604</v>
+      </c>
+      <c r="P5" s="4">
+        <v>3.178314805562774</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8574251799673623</v>
+      </c>
+      <c r="R5" s="5">
+        <v>572</v>
+      </c>
+      <c r="S5" s="5">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.153345046641502</v>
+        <v>0.09123191650480819</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1296553276552773</v>
+        <v>0.08417655533819021</v>
       </c>
       <c r="D3" s="4">
-        <v>0.139946231640896</v>
+        <v>0.08855057052245559</v>
       </c>
       <c r="E3" s="4">
-        <v>88.68803616376454</v>
+        <v>93.42634788543202</v>
       </c>
       <c r="F3" s="4">
-        <v>93.2220436374332</v>
+        <v>95.08392278379776</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.002275395919727423</v>
+      </c>
+      <c r="O3" s="5">
+        <v>902</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0912091126130779</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08412537067882105</v>
+      </c>
+      <c r="R3" s="5">
+        <v>902</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3543611908501279</v>
+        <v>2.718564590920399</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3075975229146407</v>
+        <v>0.6647650269659953</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3181859126038098</v>
+        <v>3.204001034642507</v>
       </c>
       <c r="E4" s="4">
-        <v>88.07726001934921</v>
+        <v>89.4854918451145</v>
       </c>
       <c r="F4" s="4">
-        <v>92.16578859686811</v>
+        <v>90.86120985742976</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>847</v>
+        <v>661</v>
       </c>
       <c r="I4" s="5">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="J4" s="5">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>112</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.080453739519645</v>
+      </c>
+      <c r="O4" s="5">
+        <v>773</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.871590120617022</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.410890037703731</v>
+      </c>
+      <c r="R4" s="5">
+        <v>670</v>
+      </c>
+      <c r="S4" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2604421297777951</v>
+        <v>2.014971371183639</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1420162485868962</v>
+        <v>0.1203553717364785</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2333893087293367</v>
+        <v>2.510899591506712</v>
       </c>
       <c r="E5" s="4">
-        <v>86.66965548595658</v>
+        <v>86.3714891897352</v>
       </c>
       <c r="F5" s="4">
-        <v>90.72705550756319</v>
+        <v>87.00770538463219</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>734</v>
+        <v>565</v>
       </c>
       <c r="I5" s="5">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="J5" s="5">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="L5" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M5" s="5">
-        <v>16</v>
+        <v>94</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.32523703366444</v>
+      </c>
+      <c r="O5" s="5">
+        <v>659</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.701321121786875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.350496407292254</v>
+      </c>
+      <c r="R5" s="5">
+        <v>569</v>
+      </c>
+      <c r="S5" s="5">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1583103965573736</v>
+        <v>0.1607591438398197</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1556261008657508</v>
+        <v>0.1562897876752814</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1694314976797465</v>
+        <v>0.1527518511424315</v>
       </c>
       <c r="E3" s="4">
-        <v>97.01579229318389</v>
+        <v>94.76550059074323</v>
       </c>
       <c r="F3" s="4">
-        <v>97.73614821571813</v>
+        <v>96.0178850251839</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="I3" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1485042415266403</v>
+      </c>
+      <c r="O3" s="5">
+        <v>912</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0859936900615717</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08169180333727909</v>
+      </c>
+      <c r="R3" s="5">
+        <v>912</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2884094299437134</v>
+        <v>3.112049723489646</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1610822203449254</v>
+        <v>0.5567502838159225</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4532237628051915</v>
+        <v>4.09725202065845</v>
       </c>
       <c r="E4" s="4">
-        <v>95.62439533484115</v>
+        <v>87.1514652893632</v>
       </c>
       <c r="F4" s="4">
-        <v>96.19417492753685</v>
+        <v>88.212294981349</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>836</v>
+        <v>667</v>
       </c>
       <c r="I4" s="5">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J4" s="5">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="K4" s="5">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="L4" s="5">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="M4" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.7205613532272972</v>
+      </c>
+      <c r="O4" s="5">
+        <v>681</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.676841877700531</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1857500547599551</v>
+      </c>
+      <c r="R4" s="5">
+        <v>667</v>
+      </c>
+      <c r="S4" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6180287203309183</v>
+        <v>1.762780696314527</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3892871550988564</v>
+        <v>0.2036587347705409</v>
       </c>
       <c r="D5" s="4">
-        <v>0.742538081068746</v>
+        <v>3.361708231014246</v>
       </c>
       <c r="E5" s="4">
-        <v>94.39108068970143</v>
+        <v>83.5375412541254</v>
       </c>
       <c r="F5" s="4">
-        <v>95.00337785456381</v>
+        <v>84.57176002835203</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>723</v>
+        <v>592</v>
       </c>
       <c r="I5" s="5">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J5" s="5">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="K5" s="5">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="L5" s="5">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="M5" s="5">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.077136963486872</v>
+      </c>
+      <c r="O5" s="5">
+        <v>606</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.800543682063408</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2718783695871222</v>
+      </c>
+      <c r="R5" s="5">
+        <v>592</v>
+      </c>
+      <c r="S5" s="5">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1552411974458367</v>
+        <v>0.153345046641502</v>
       </c>
       <c r="C3" s="4">
-        <v>0.133040652871854</v>
+        <v>0.1296553276552773</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1429330118064599</v>
+        <v>0.139946231640896</v>
       </c>
       <c r="E3" s="4">
-        <v>89.01133053005455</v>
+        <v>88.68803616376454</v>
       </c>
       <c r="F3" s="4">
-        <v>93.31202382417612</v>
+        <v>93.2220436374332</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
@@ -2765,105 +3342,159 @@
         <v>887</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K3" s="5">
         <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1176525444832861</v>
+      </c>
+      <c r="O3" s="5">
+        <v>887</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08168149122507344</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05375479000831144</v>
+      </c>
+      <c r="R3" s="5">
+        <v>887</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2337951830236103</v>
+        <v>0.3543611908501279</v>
       </c>
       <c r="C4" s="4">
-        <v>0.199437934976236</v>
+        <v>0.3075975229146407</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2224343852990784</v>
+        <v>0.3181859126038098</v>
       </c>
       <c r="E4" s="4">
-        <v>88.4176626977781</v>
+        <v>88.07726001934921</v>
       </c>
       <c r="F4" s="4">
-        <v>92.51313346911485</v>
+        <v>92.16578859686811</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="I4" s="5">
         <v>14</v>
       </c>
       <c r="J4" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3042899452663385</v>
+      </c>
+      <c r="O4" s="5">
+        <v>847</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1508198978401864</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1045944061445474</v>
+      </c>
+      <c r="R4" s="5">
+        <v>847</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2828577713663818</v>
+        <v>0.2604421297777951</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1554742655504352</v>
+        <v>0.1420162485868962</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2494641970119543</v>
+        <v>0.2333893087293367</v>
       </c>
       <c r="E5" s="4">
-        <v>86.56163703104993</v>
+        <v>86.66965548595658</v>
       </c>
       <c r="F5" s="4">
-        <v>90.52713912330663</v>
+        <v>90.72705550756319</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="I5" s="5">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J5" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="5">
         <v>4</v>
       </c>
       <c r="L5" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="5">
         <v>16</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.04839494755280598</v>
+      </c>
+      <c r="O5" s="5">
+        <v>750</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2325846200411077</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1089498809115319</v>
+      </c>
+      <c r="R5" s="5">
+        <v>734</v>
+      </c>
+      <c r="S5" s="5">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3597,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.069793019290112</v>
+        <v>0.1583103965573736</v>
       </c>
       <c r="C3" s="4">
-        <v>0.06496804562580862</v>
+        <v>0.1556261008657508</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06693740969553058</v>
+        <v>0.1694314976797465</v>
       </c>
       <c r="E3" s="4">
-        <v>95.98378941652132</v>
+        <v>97.01579229318389</v>
       </c>
       <c r="F3" s="4">
-        <v>96.94023925534869</v>
+        <v>97.73614821571813</v>
       </c>
       <c r="G3" s="5">
         <v>927</v>
       </c>
       <c r="H3" s="5">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="I3" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
         <v>6</v>
@@ -2992,91 +3656,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1545227498594684</v>
+      </c>
+      <c r="O3" s="5">
+        <v>916</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05840847492469877</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05565388151630912</v>
+      </c>
+      <c r="R3" s="5">
+        <v>916</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.573389733062818</v>
+        <v>0.2884094299437134</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1559153967606837</v>
+        <v>0.1610822203449254</v>
       </c>
       <c r="D4" s="4">
-        <v>2.757549803797838</v>
+        <v>0.4532237628051915</v>
       </c>
       <c r="E4" s="4">
-        <v>90.33960280640814</v>
+        <v>95.62439533484115</v>
       </c>
       <c r="F4" s="4">
-        <v>91.57641712449076</v>
+        <v>96.19417492753685</v>
       </c>
       <c r="G4" s="5">
         <v>893</v>
       </c>
       <c r="H4" s="5">
-        <v>723</v>
+        <v>836</v>
       </c>
       <c r="I4" s="5">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J4" s="5">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="K4" s="5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M4" s="5">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>15</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.06357013484805947</v>
+      </c>
+      <c r="O4" s="5">
+        <v>851</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2472712154168003</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1159985150874442</v>
+      </c>
+      <c r="R4" s="5">
+        <v>836</v>
+      </c>
+      <c r="S4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.380585090371597</v>
+        <v>0.6180287203309183</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1903961254411317</v>
+        <v>0.3892871550988564</v>
       </c>
       <c r="D5" s="4">
-        <v>2.924815592958169</v>
+        <v>0.742538081068746</v>
       </c>
       <c r="E5" s="4">
-        <v>88.17968276419475</v>
+        <v>94.39108068970143</v>
       </c>
       <c r="F5" s="4">
-        <v>88.83396183578046</v>
+        <v>95.00337785456381</v>
       </c>
       <c r="G5" s="5">
         <v>808</v>
       </c>
       <c r="H5" s="5">
-        <v>634</v>
+        <v>723</v>
       </c>
       <c r="I5" s="5">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="K5" s="5">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="L5" s="5">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="M5" s="5">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3008409244280677</v>
+      </c>
+      <c r="O5" s="5">
+        <v>759</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3708021725290634</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1121574624877428</v>
+      </c>
+      <c r="R5" s="5">
+        <v>722</v>
+      </c>
+      <c r="S5" s="5">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1552411974458367</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.133040652871854</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1429330118064599</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.01133053005455</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.31202382417612</v>
+      </c>
+      <c r="G3" s="5">
+        <v>927</v>
+      </c>
+      <c r="H3" s="5">
+        <v>887</v>
+      </c>
+      <c r="I3" s="5">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5">
+        <v>32</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.1184093683526064</v>
+      </c>
+      <c r="O3" s="5">
+        <v>887</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08744806846074012</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06096582809511136</v>
+      </c>
+      <c r="R3" s="5">
+        <v>887</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2337951830236103</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.199437934976236</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2224343852990784</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.4176626977781</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.51313346911485</v>
+      </c>
+      <c r="G4" s="5">
+        <v>893</v>
+      </c>
+      <c r="H4" s="5">
+        <v>849</v>
+      </c>
+      <c r="I4" s="5">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5">
+        <v>30</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
+        <v>27</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1647925511081258</v>
+      </c>
+      <c r="O4" s="5">
+        <v>849</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1499922163048936</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1097595923524725</v>
+      </c>
+      <c r="R4" s="5">
+        <v>849</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2828577713663818</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1554742655504352</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2494641970119543</v>
+      </c>
+      <c r="E5" s="4">
+        <v>86.56163703104993</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.52713912330663</v>
+      </c>
+      <c r="G5" s="5">
+        <v>808</v>
+      </c>
+      <c r="H5" s="5">
+        <v>728</v>
+      </c>
+      <c r="I5" s="5">
+        <v>35</v>
+      </c>
+      <c r="J5" s="5">
+        <v>45</v>
+      </c>
+      <c r="K5" s="5">
+        <v>4</v>
+      </c>
+      <c r="L5" s="5">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5">
+        <v>16</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.0740795643652709</v>
+      </c>
+      <c r="O5" s="5">
+        <v>744</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2399371899440081</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1032569483352546</v>
+      </c>
+      <c r="R5" s="5">
+        <v>728</v>
+      </c>
+      <c r="S5" s="5">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.069793019290112</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.06496804562580862</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.06693740969553058</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.98378941652132</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.94023925534869</v>
+      </c>
+      <c r="G3" s="5">
+        <v>927</v>
+      </c>
+      <c r="H3" s="5">
+        <v>911</v>
+      </c>
+      <c r="I3" s="5">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.02725744240390541</v>
+      </c>
+      <c r="O3" s="5">
+        <v>911</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06610130235708273</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06146928905572296</v>
+      </c>
+      <c r="R3" s="5">
+        <v>911</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.573389733062818</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1559153967606837</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.757549803797838</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90.33960280640814</v>
+      </c>
+      <c r="F4" s="4">
+        <v>91.57641712449076</v>
+      </c>
+      <c r="G4" s="5">
+        <v>893</v>
+      </c>
+      <c r="H4" s="5">
+        <v>723</v>
+      </c>
+      <c r="I4" s="5">
+        <v>29</v>
+      </c>
+      <c r="J4" s="5">
+        <v>141</v>
+      </c>
+      <c r="K4" s="5">
+        <v>50</v>
+      </c>
+      <c r="L4" s="5">
+        <v>55</v>
+      </c>
+      <c r="M4" s="5">
+        <v>36</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.5504812285231078</v>
+      </c>
+      <c r="O4" s="5">
+        <v>759</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.81912977691015</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5475778540501073</v>
+      </c>
+      <c r="R4" s="5">
+        <v>725</v>
+      </c>
+      <c r="S4" s="5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.380585090371597</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1903961254411317</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2.924815592958169</v>
+      </c>
+      <c r="E5" s="4">
+        <v>88.17968276419475</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.83396183578046</v>
+      </c>
+      <c r="G5" s="5">
+        <v>808</v>
+      </c>
+      <c r="H5" s="5">
+        <v>634</v>
+      </c>
+      <c r="I5" s="5">
+        <v>58</v>
+      </c>
+      <c r="J5" s="5">
+        <v>116</v>
+      </c>
+      <c r="K5" s="5">
+        <v>41</v>
+      </c>
+      <c r="L5" s="5">
+        <v>42</v>
+      </c>
+      <c r="M5" s="5">
+        <v>33</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4316319560934572</v>
+      </c>
+      <c r="O5" s="5">
+        <v>667</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.62390255172819</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5573806862063017</v>
+      </c>
+      <c r="R5" s="5">
+        <v>634</v>
+      </c>
+      <c r="S5" s="5">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>80.70776255707763</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4.26179604261796</v>
+      </c>
+      <c r="D3" s="3">
+        <v>15.03044140030442</v>
+      </c>
+      <c r="E3" s="3">
+        <v>7.267884322678843</v>
+      </c>
+      <c r="F3" s="3">
+        <v>6.126331811263317</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.636225266362253</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.603839398119619</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2503887752842477</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.460112327675686</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.1932485322896</v>
+      </c>
+      <c r="L3" s="4">
+        <v>87.36827028830793</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N3" s="5">
+        <v>26032969.26736832</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.65454603523863</v>
+      </c>
+      <c r="P3" s="5">
+        <v>773535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>81.39269406392694</v>
+      </c>
+      <c r="C4" s="3">
+        <v>11.49162861491629</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.115677321156773</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.8751902587519025</v>
+      </c>
+      <c r="F4" s="3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.684931506849315</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3729118252549304</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3080361107466925</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3790126744400553</v>
+      </c>
+      <c r="K4" s="4">
+        <v>81.84100580871623</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.31244147521625</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N4" s="5">
+        <v>10199123.42691422</v>
+      </c>
+      <c r="O4" s="4">
+        <v>39.73029160221969</v>
+      </c>
+      <c r="P4" s="5">
+        <v>256709</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>89.15525114155251</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.06697108066971</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.36986301369863</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.006088280060883</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3.691019786910198</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.8869655227861335</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3572363640778014</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.368039205131769</v>
+      </c>
+      <c r="K5" s="4">
+        <v>91.19033381998136</v>
+      </c>
+      <c r="L5" s="4">
+        <v>93.19242267918368</v>
+      </c>
+      <c r="M5" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N5" s="5">
+        <v>22966771.95239067</v>
+      </c>
+      <c r="O5" s="4">
+        <v>123.858833677893</v>
+      </c>
+      <c r="P5" s="5">
+        <v>185427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>83.67579908675799</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8.181126331811264</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.143074581430746</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.06544901065449</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.794520547945205</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.28310502283105</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.6259276687395378</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3137198006770681</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.8256905300766807</v>
+      </c>
+      <c r="K6" s="4">
+        <v>82.97303243976449</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.80279744210502</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N6" s="5">
+        <v>23381594.02370453</v>
+      </c>
+      <c r="O6" s="4">
+        <v>89.14915269737692</v>
+      </c>
+      <c r="P6" s="5">
+        <v>262275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>83.94216133942162</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.560121765601218</v>
+      </c>
+      <c r="D7" s="3">
+        <v>14.49771689497717</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6.202435312024352</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.5662100456621</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.729071537290715</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.925092631974459</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4152786041209838</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.506180676103521</v>
+      </c>
+      <c r="K7" s="4">
+        <v>91.44940929187509</v>
+      </c>
+      <c r="L7" s="4">
+        <v>92.80040877965376</v>
+      </c>
+      <c r="M7" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N7" s="5">
+        <v>72489676.7809391</v>
+      </c>
+      <c r="O7" s="4">
+        <v>146.0843354754142</v>
+      </c>
+      <c r="P7" s="5">
+        <v>496218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>83.0289193302892</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.680365296803653</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12.29071537290715</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.560121765601218</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7.229832572298325</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3.50076103500761</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.022242104555708</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2498225050975524</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.558108618327527</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.70869961378773</v>
+      </c>
+      <c r="L8" s="4">
+        <v>89.95320145464932</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N8" s="5">
+        <v>4227940.214633942</v>
+      </c>
+      <c r="O8" s="4">
+        <v>10.75409507037811</v>
+      </c>
+      <c r="P8" s="5">
+        <v>393147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75.98934550989345</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12.13850837138508</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11.87214611872146</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.76103500761035</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7.686453576864535</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.424657534246575</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6400165041591689</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.364640460960513</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.7400597039316763</v>
+      </c>
+      <c r="K9" s="4">
+        <v>80.37694529866741</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.71554486360951</v>
+      </c>
+      <c r="M9" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N9" s="5">
+        <v>8126507.363557816</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.8160274570557</v>
+      </c>
+      <c r="P9" s="5">
+        <v>272555</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>92.12328767123287</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.598173515981735</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6.278538812785388</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.30441400304414</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5.707762557077626</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.2663622526636225</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1850277775921205</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1405527223346537</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1806834117579051</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.48489319624339</v>
+      </c>
+      <c r="L10" s="4">
+        <v>91.39037861065988</v>
+      </c>
+      <c r="M10" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N10" s="5">
+        <v>12744143.59974861</v>
+      </c>
+      <c r="O10" s="4">
+        <v>83.78792636258127</v>
+      </c>
+      <c r="P10" s="5">
+        <v>152100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>80.28919330289193</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.32724505327245</v>
+      </c>
+      <c r="D11" s="3">
+        <v>14.38356164383562</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.098934550989346</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.30593607305936</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1.97869101978691</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2.344289930510119</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4421771765360566</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3.110305103910154</v>
+      </c>
+      <c r="K11" s="4">
+        <v>85.45979198376453</v>
+      </c>
+      <c r="L11" s="4">
+        <v>87.5539619788954</v>
+      </c>
+      <c r="M11" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N11" s="5">
+        <v>22593649.86181259</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.2749302705562</v>
+      </c>
+      <c r="P11" s="5">
+        <v>575269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>81.46879756468797</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5.93607305936073</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12.5951293759513</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.43531202435312</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.815829528158295</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7.343987823439877</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.838488695398447</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.8358756961060667</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2.125875047597869</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.91816285113737</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.1659371286336</v>
+      </c>
+      <c r="M12" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4103689.419269562</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.19384519034307</v>
+      </c>
+      <c r="P12" s="5">
+        <v>238672</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>82.6103500761035</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.41400304414003</v>
+      </c>
+      <c r="D13" s="3">
+        <v>12.97564687975647</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5.859969558599695</v>
+      </c>
+      <c r="F13" s="3">
+        <v>6.050228310502283</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1.06544901065449</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1.49352178180399</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1655228954233371</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.305471194077953</v>
+      </c>
+      <c r="K13" s="4">
+        <v>88.72610764244811</v>
+      </c>
+      <c r="L13" s="4">
+        <v>89.8463245584464</v>
+      </c>
+      <c r="M13" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N13" s="5">
+        <v>54055671.13518715</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.53065933781134</v>
+      </c>
+      <c r="P13" s="5">
+        <v>725281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>93.91171993911721</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.788432267884323</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.299847792998477</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.4185692541856925</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.272450532724505</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.60882800608828</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1515712648897049</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.08761797946955768</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1251559532766653</v>
+      </c>
+      <c r="K14" s="4">
+        <v>87.85992555317405</v>
+      </c>
+      <c r="L14" s="4">
+        <v>92.09602150647424</v>
+      </c>
+      <c r="M14" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N14" s="5">
+        <v>35163771.80409431</v>
+      </c>
+      <c r="O14" s="4">
+        <v>213.0840658822971</v>
+      </c>
+      <c r="P14" s="5">
+        <v>165023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>94.1400304414003</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.5220700152207</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4.337899543378995</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.91324200913242</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.445966514459665</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.97869101978691</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2186324227647951</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.09253492400897043</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.3241583307291821</v>
+      </c>
+      <c r="K15" s="4">
+        <v>95.73600368610154</v>
+      </c>
+      <c r="L15" s="4">
+        <v>96.37196990591785</v>
+      </c>
+      <c r="M15" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N15" s="5">
+        <v>23932042.4258709</v>
+      </c>
+      <c r="O15" s="4">
+        <v>208.7527579169325</v>
+      </c>
+      <c r="P15" s="5">
+        <v>114643</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>93.75951293759512</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.168949771689498</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.071537290715373</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.380517503805175</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.082191780821918</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.60882800608828</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1555847253037042</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.09027339359402527</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1272706127858137</v>
+      </c>
+      <c r="K16" s="4">
+        <v>88.05642272129553</v>
+      </c>
+      <c r="L16" s="4">
+        <v>92.18432370036645</v>
+      </c>
+      <c r="M16" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N16" s="5">
+        <v>15794681.76436424</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.77264393428607</v>
+      </c>
+      <c r="P16" s="5">
+        <v>161545</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>86.37747336377474</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.691019786910198</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9.931506849315069</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.50076103500761</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.881278538812785</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2.549467275494673</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.140742792946026</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3552298773440029</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.996634691105638</v>
+      </c>
+      <c r="K17" s="4">
+        <v>91.66644663953859</v>
+      </c>
+      <c r="L17" s="4">
+        <v>92.62526006285759</v>
+      </c>
+      <c r="M17" s="5">
+        <v>2628</v>
+      </c>
+      <c r="N17" s="5">
+        <v>28048055.89914322</v>
+      </c>
+      <c r="O17" s="4">
+        <v>96.4066059399633</v>
+      </c>
+      <c r="P17" s="5">
+        <v>290935</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,16 +5382,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="L3" s="5">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3250,16 +5426,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M4" s="5">
         <v>2</v>
       </c>
       <c r="N4" s="5">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3294,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="M5" s="5">
         <v>3</v>
@@ -3338,16 +5514,16 @@
         <v>2</v>
       </c>
       <c r="K6" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L6" s="5">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="M6" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3382,16 +5558,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="L7" s="5">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3426,10 +5602,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="L8" s="5">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3470,16 +5646,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L9" s="5">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3514,16 +5690,16 @@
         <v>3</v>
       </c>
       <c r="K10" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="5">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3558,16 +5734,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="L11" s="5">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3602,16 +5778,16 @@
         <v>3</v>
       </c>
       <c r="K12" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="M12" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3646,10 +5822,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="L13" s="5">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3690,16 +5866,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3734,16 +5910,16 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>34</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
         <v>5</v>
-      </c>
-      <c r="L15" s="5">
-        <v>48</v>
-      </c>
-      <c r="M15" s="5">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3778,16 +5954,16 @@
         <v>3</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3822,13 +5998,13 @@
         <v>2</v>
       </c>
       <c r="K17" s="5">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L17" s="5">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="M17" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" s="5">
         <v>6</v>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2121</v>
+      </c>
+      <c r="C3" s="5">
+        <v>112</v>
+      </c>
+      <c r="D3" s="5">
+        <v>395</v>
+      </c>
+      <c r="E3" s="5">
+        <v>191</v>
+      </c>
+      <c r="F3" s="5">
+        <v>161</v>
+      </c>
+      <c r="G3" s="5">
+        <v>43</v>
+      </c>
+      <c r="H3" s="5">
+        <v>191</v>
+      </c>
+      <c r="I3" s="5">
+        <v>191</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>57</v>
+      </c>
+      <c r="L3" s="5">
+        <v>120</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2139</v>
+      </c>
+      <c r="C4" s="5">
+        <v>302</v>
+      </c>
+      <c r="D4" s="5">
+        <v>187</v>
+      </c>
+      <c r="E4" s="5">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5">
+        <v>146</v>
+      </c>
+      <c r="G4" s="5">
+        <v>18</v>
+      </c>
+      <c r="H4" s="5">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5">
+        <v>23</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>115</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2343</v>
+      </c>
+      <c r="C5" s="5">
+        <v>73</v>
+      </c>
+      <c r="D5" s="5">
+        <v>212</v>
+      </c>
+      <c r="E5" s="5">
+        <v>36</v>
+      </c>
+      <c r="F5" s="5">
+        <v>79</v>
+      </c>
+      <c r="G5" s="5">
+        <v>97</v>
+      </c>
+      <c r="H5" s="5">
+        <v>36</v>
+      </c>
+      <c r="I5" s="5">
+        <v>36</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5">
+        <v>74</v>
+      </c>
+      <c r="M5" s="5">
+        <v>3</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2199</v>
+      </c>
+      <c r="C6" s="5">
+        <v>215</v>
+      </c>
+      <c r="D6" s="5">
+        <v>214</v>
+      </c>
+      <c r="E6" s="5">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5">
+        <v>126</v>
+      </c>
+      <c r="G6" s="5">
+        <v>60</v>
+      </c>
+      <c r="H6" s="5">
+        <v>28</v>
+      </c>
+      <c r="I6" s="5">
+        <v>26</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>5</v>
+      </c>
+      <c r="L6" s="5">
+        <v>116</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2206</v>
+      </c>
+      <c r="C7" s="5">
+        <v>41</v>
+      </c>
+      <c r="D7" s="5">
+        <v>381</v>
+      </c>
+      <c r="E7" s="5">
+        <v>163</v>
+      </c>
+      <c r="F7" s="5">
+        <v>120</v>
+      </c>
+      <c r="G7" s="5">
+        <v>98</v>
+      </c>
+      <c r="H7" s="5">
+        <v>163</v>
+      </c>
+      <c r="I7" s="5">
+        <v>163</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>16</v>
+      </c>
+      <c r="L7" s="5">
+        <v>100</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2182</v>
+      </c>
+      <c r="C8" s="5">
+        <v>123</v>
+      </c>
+      <c r="D8" s="5">
+        <v>323</v>
+      </c>
+      <c r="E8" s="5">
+        <v>41</v>
+      </c>
+      <c r="F8" s="5">
+        <v>190</v>
+      </c>
+      <c r="G8" s="5">
+        <v>92</v>
+      </c>
+      <c r="H8" s="5">
+        <v>41</v>
+      </c>
+      <c r="I8" s="5">
+        <v>41</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>43</v>
+      </c>
+      <c r="L8" s="5">
+        <v>150</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1997</v>
+      </c>
+      <c r="C9" s="5">
+        <v>319</v>
+      </c>
+      <c r="D9" s="5">
+        <v>312</v>
+      </c>
+      <c r="E9" s="5">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5">
+        <v>202</v>
+      </c>
+      <c r="G9" s="5">
+        <v>90</v>
+      </c>
+      <c r="H9" s="5">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5">
+        <v>20</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="5">
+        <v>183</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2421</v>
+      </c>
+      <c r="C10" s="5">
+        <v>42</v>
+      </c>
+      <c r="D10" s="5">
+        <v>165</v>
+      </c>
+      <c r="E10" s="5">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5">
+        <v>150</v>
+      </c>
+      <c r="G10" s="5">
+        <v>7</v>
+      </c>
+      <c r="H10" s="5">
+        <v>8</v>
+      </c>
+      <c r="I10" s="5">
+        <v>6</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5">
+        <v>4</v>
+      </c>
+      <c r="L10" s="5">
+        <v>128</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2110</v>
+      </c>
+      <c r="C11" s="5">
+        <v>140</v>
+      </c>
+      <c r="D11" s="5">
+        <v>378</v>
+      </c>
+      <c r="E11" s="5">
+        <v>134</v>
+      </c>
+      <c r="F11" s="5">
+        <v>192</v>
+      </c>
+      <c r="G11" s="5">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5">
+        <v>134</v>
+      </c>
+      <c r="I11" s="5">
+        <v>134</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>39</v>
+      </c>
+      <c r="L11" s="5">
+        <v>157</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2141</v>
+      </c>
+      <c r="C12" s="5">
+        <v>156</v>
+      </c>
+      <c r="D12" s="5">
+        <v>331</v>
+      </c>
+      <c r="E12" s="5">
+        <v>64</v>
+      </c>
+      <c r="F12" s="5">
+        <v>74</v>
+      </c>
+      <c r="G12" s="5">
+        <v>193</v>
+      </c>
+      <c r="H12" s="5">
+        <v>64</v>
+      </c>
+      <c r="I12" s="5">
+        <v>61</v>
+      </c>
+      <c r="J12" s="5">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>4</v>
+      </c>
+      <c r="L12" s="5">
+        <v>65</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2171</v>
+      </c>
+      <c r="C13" s="5">
+        <v>116</v>
+      </c>
+      <c r="D13" s="5">
+        <v>341</v>
+      </c>
+      <c r="E13" s="5">
+        <v>154</v>
+      </c>
+      <c r="F13" s="5">
+        <v>159</v>
+      </c>
+      <c r="G13" s="5">
+        <v>28</v>
+      </c>
+      <c r="H13" s="5">
+        <v>154</v>
+      </c>
+      <c r="I13" s="5">
+        <v>154</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>63</v>
+      </c>
+      <c r="L13" s="5">
+        <v>109</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2468</v>
+      </c>
+      <c r="C14" s="5">
+        <v>47</v>
+      </c>
+      <c r="D14" s="5">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5">
+        <v>11</v>
+      </c>
+      <c r="F14" s="5">
+        <v>86</v>
+      </c>
+      <c r="G14" s="5">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5">
+        <v>11</v>
+      </c>
+      <c r="I14" s="5">
+        <v>9</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>78</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2474</v>
+      </c>
+      <c r="C15" s="5">
+        <v>40</v>
+      </c>
+      <c r="D15" s="5">
+        <v>114</v>
+      </c>
+      <c r="E15" s="5">
+        <v>24</v>
+      </c>
+      <c r="F15" s="5">
+        <v>38</v>
+      </c>
+      <c r="G15" s="5">
+        <v>52</v>
+      </c>
+      <c r="H15" s="5">
+        <v>24</v>
+      </c>
+      <c r="I15" s="5">
+        <v>24</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>34</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2464</v>
+      </c>
+      <c r="C16" s="5">
+        <v>57</v>
+      </c>
+      <c r="D16" s="5">
+        <v>107</v>
+      </c>
+      <c r="E16" s="5">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5">
+        <v>81</v>
+      </c>
+      <c r="G16" s="5">
+        <v>16</v>
+      </c>
+      <c r="H16" s="5">
+        <v>10</v>
+      </c>
+      <c r="I16" s="5">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>71</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2270</v>
+      </c>
+      <c r="C17" s="5">
+        <v>97</v>
+      </c>
+      <c r="D17" s="5">
+        <v>261</v>
+      </c>
+      <c r="E17" s="5">
+        <v>92</v>
+      </c>
+      <c r="F17" s="5">
+        <v>102</v>
+      </c>
+      <c r="G17" s="5">
+        <v>67</v>
+      </c>
+      <c r="H17" s="5">
+        <v>92</v>
+      </c>
+      <c r="I17" s="5">
+        <v>91</v>
+      </c>
+      <c r="J17" s="5">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5">
+        <v>10</v>
+      </c>
+      <c r="L17" s="5">
+        <v>90</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1471352879882628</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07952600696503768</v>
+      </c>
+      <c r="O3" s="5">
+        <v>902</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.127594317313434</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1197876135305364</v>
+      </c>
+      <c r="R3" s="5">
+        <v>902</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.894953101481558</v>
@@ -4001,10 +6982,28 @@
       <c r="M4" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6940438841340045</v>
+      </c>
+      <c r="O4" s="5">
+        <v>682</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.595194324235674</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2929372889088343</v>
+      </c>
+      <c r="R4" s="5">
+        <v>662</v>
+      </c>
+      <c r="S4" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.115730054369898</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>23</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4807830131816727</v>
+      </c>
+      <c r="O5" s="5">
+        <v>580</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.201858260601917</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4113136081071763</v>
+      </c>
+      <c r="R5" s="5">
+        <v>557</v>
+      </c>
+      <c r="S5" s="5">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2241442907269783</v>
@@ -4173,10 +7223,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1418326304085579</v>
+      </c>
+      <c r="O3" s="5">
+        <v>818</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2116049344070962</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2066701186441467</v>
+      </c>
+      <c r="R3" s="5">
+        <v>818</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6422338022969426</v>
@@ -4214,10 +7282,28 @@
       <c r="M4" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5441005212699151</v>
+      </c>
+      <c r="O4" s="5">
+        <v>770</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4778455021642342</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4313050510100551</v>
+      </c>
+      <c r="R4" s="5">
+        <v>767</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5231217920640083</v>
@@ -4255,9 +7341,27 @@
       <c r="M5" s="5">
         <v>15</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2899082436118227</v>
+      </c>
+      <c r="O5" s="5">
+        <v>569</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4420030558687104</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2870435193349296</v>
+      </c>
+      <c r="R5" s="5">
+        <v>554</v>
+      </c>
+      <c r="S5" s="5">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7464,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.08877061566832382</v>
@@ -4386,10 +7523,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01665483512680748</v>
+      </c>
+      <c r="O3" s="5">
+        <v>906</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0874347811056862</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08143020088285033</v>
+      </c>
+      <c r="R3" s="5">
+        <v>906</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.015258134809099</v>
@@ -4427,10 +7582,28 @@
       <c r="M4" s="5">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.293570856884371</v>
+      </c>
+      <c r="O4" s="5">
+        <v>791</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.975888766367197</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7726321898742268</v>
+      </c>
+      <c r="R4" s="5">
+        <v>739</v>
+      </c>
+      <c r="S4" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.533759873282359</v>
@@ -4468,9 +7641,27 @@
       <c r="M5" s="5">
         <v>44</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1360325530645945</v>
+      </c>
+      <c r="O5" s="5">
+        <v>743</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6007731230582685</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2754353162140007</v>
+      </c>
+      <c r="R5" s="5">
+        <v>698</v>
+      </c>
+      <c r="S5" s="5">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7764,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2096766583860661</v>
@@ -4599,10 +7823,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1367307879189856</v>
+      </c>
+      <c r="O3" s="5">
+        <v>880</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1709549019958447</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1620522584643504</v>
+      </c>
+      <c r="R3" s="5">
+        <v>880</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.631914553762885</v>
@@ -4640,10 +7882,28 @@
       <c r="M4" s="5">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.283885810032353</v>
+      </c>
+      <c r="O4" s="5">
+        <v>743</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.143460215702502</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5043890735198354</v>
+      </c>
+      <c r="R4" s="5">
+        <v>701</v>
+      </c>
+      <c r="S4" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5774248877609969</v>
@@ -4681,9 +7941,27 @@
       <c r="M5" s="5">
         <v>26</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2010141678128688</v>
+      </c>
+      <c r="O5" s="5">
+        <v>636</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5759316171720582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3134095690984464</v>
+      </c>
+      <c r="R5" s="5">
+        <v>618</v>
+      </c>
+      <c r="S5" s="5">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8064,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.05671636922493888</v>
@@ -4812,10 +8123,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02264211352126358</v>
+      </c>
+      <c r="O3" s="5">
+        <v>916</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0523291474879299</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04705361015301595</v>
+      </c>
+      <c r="R3" s="5">
+        <v>916</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>3.163393298936458</v>
@@ -4853,10 +8182,28 @@
       <c r="M4" s="5">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.069910084373121</v>
+      </c>
+      <c r="O4" s="5">
+        <v>736</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.990761237546193</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5648908010719612</v>
+      </c>
+      <c r="R4" s="5">
+        <v>692</v>
+      </c>
+      <c r="S4" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.490404519897883</v>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>54</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.7856910444720416</v>
+      </c>
+      <c r="O5" s="5">
+        <v>652</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.895896697993588</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8061857181420243</v>
+      </c>
+      <c r="R5" s="5">
+        <v>598</v>
+      </c>
+      <c r="S5" s="5">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.09286467622510093</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.08668988542441851</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.08859044858370471</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.9801422186997</v>
-      </c>
-      <c r="F3" s="4">
-        <v>95.63648583750157</v>
-      </c>
-      <c r="G3" s="5">
-        <v>927</v>
-      </c>
-      <c r="H3" s="5">
-        <v>906</v>
-      </c>
-      <c r="I3" s="5">
-        <v>7</v>
-      </c>
-      <c r="J3" s="5">
-        <v>14</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>12</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.013630059449546</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.588218197755032</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2.894651392712531</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.87010078387461</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.06726941586483</v>
-      </c>
-      <c r="G4" s="5">
-        <v>893</v>
-      </c>
-      <c r="H4" s="5">
-        <v>675</v>
-      </c>
-      <c r="I4" s="5">
-        <v>38</v>
-      </c>
-      <c r="J4" s="5">
-        <v>180</v>
-      </c>
-      <c r="K4" s="5">
-        <v>23</v>
-      </c>
-      <c r="L4" s="5">
-        <v>99</v>
-      </c>
-      <c r="M4" s="5">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.284036689854188</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1312646933949465</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.158448499100866</v>
-      </c>
-      <c r="E5" s="4">
-        <v>84.69290934195463</v>
-      </c>
-      <c r="F5" s="4">
-        <v>85.51722705827623</v>
-      </c>
-      <c r="G5" s="5">
-        <v>808</v>
-      </c>
-      <c r="H5" s="5">
-        <v>587</v>
-      </c>
-      <c r="I5" s="5">
-        <v>78</v>
-      </c>
-      <c r="J5" s="5">
-        <v>143</v>
-      </c>
-      <c r="K5" s="5">
-        <v>16</v>
-      </c>
-      <c r="L5" s="5">
-        <v>79</v>
-      </c>
-      <c r="M5" s="5">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2679302675028883</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.249439555906455</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2273639727727229</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.07282654161972</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.91230762919082</v>
-      </c>
-      <c r="G3" s="5">
-        <v>927</v>
-      </c>
-      <c r="H3" s="5">
-        <v>851</v>
-      </c>
-      <c r="I3" s="5">
-        <v>40</v>
-      </c>
-      <c r="J3" s="5">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>35</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.502621592863205</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8073037352511382</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.805827755950185</v>
-      </c>
-      <c r="E4" s="4">
-        <v>79.7658279437196</v>
-      </c>
-      <c r="F4" s="4">
-        <v>83.07333198052997</v>
-      </c>
-      <c r="G4" s="5">
-        <v>893</v>
-      </c>
-      <c r="H4" s="5">
-        <v>585</v>
-      </c>
-      <c r="I4" s="5">
-        <v>114</v>
-      </c>
-      <c r="J4" s="5">
-        <v>194</v>
-      </c>
-      <c r="K4" s="5">
-        <v>6</v>
-      </c>
-      <c r="L4" s="5">
-        <v>87</v>
-      </c>
-      <c r="M4" s="5">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7553044495602922</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3922027002254465</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.015622506875911</v>
-      </c>
-      <c r="E5" s="4">
-        <v>76.81215060281531</v>
-      </c>
-      <c r="F5" s="4">
-        <v>79.610466919175</v>
-      </c>
-      <c r="G5" s="5">
-        <v>808</v>
-      </c>
-      <c r="H5" s="5">
-        <v>518</v>
-      </c>
-      <c r="I5" s="5">
-        <v>165</v>
-      </c>
-      <c r="J5" s="5">
-        <v>125</v>
-      </c>
-      <c r="K5" s="5">
-        <v>13</v>
-      </c>
-      <c r="L5" s="5">
-        <v>80</v>
-      </c>
-      <c r="M5" s="5">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/AlonsoStrain2023.xlsx
+++ b/public/downloads/AlonsoStrain2023.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.003619283792173898</v>
+        <v>0.00570079489939479</v>
       </c>
       <c r="O3" s="5">
         <v>906</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09279800302524552</v>
+        <v>0.09279170024202681</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08658571366901505</v>
+        <v>0.08655858753214007</v>
       </c>
       <c r="R3" s="5">
         <v>906</v>
@@ -1616,16 +1616,16 @@
         <v>58</v>
       </c>
       <c r="N4" s="4">
-        <v>0.9375551521379093</v>
+        <v>0.59701191433048</v>
       </c>
       <c r="O4" s="5">
         <v>733</v>
       </c>
       <c r="P4" s="4">
-        <v>1.651154583878645</v>
+        <v>1.568472535920416</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3719211319241655</v>
+        <v>0.1869449797720189</v>
       </c>
       <c r="R4" s="5">
         <v>685</v>
@@ -1675,22 +1675,22 @@
         <v>48</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3238937692369147</v>
+        <v>0.01217034946572593</v>
       </c>
       <c r="O5" s="5">
         <v>635</v>
       </c>
       <c r="P5" s="4">
-        <v>1.393499329906395</v>
+        <v>1.28225661489716</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3585449647558011</v>
+        <v>0.1315097870805919</v>
       </c>
       <c r="R5" s="5">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="S5" s="5">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2044059334387915</v>
+        <v>-0.1874583699172945</v>
       </c>
       <c r="O3" s="5">
         <v>851</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2016688685529673</v>
+        <v>0.2016719101679769</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1903024239249593</v>
+        <v>0.1896329352947825</v>
       </c>
       <c r="R3" s="5">
         <v>851</v>
@@ -1916,22 +1916,22 @@
         <v>101</v>
       </c>
       <c r="N4" s="4">
-        <v>1.247397173131994</v>
+        <v>0.8415630475965372</v>
       </c>
       <c r="O4" s="5">
         <v>686</v>
       </c>
       <c r="P4" s="4">
-        <v>1.015137207472956</v>
+        <v>0.9619988406016615</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5704116245415298</v>
+        <v>0.3994373945384755</v>
       </c>
       <c r="R4" s="5">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="S4" s="5">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -1975,22 +1975,22 @@
         <v>32</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3666159674361618</v>
+        <v>0.1802942541226003</v>
       </c>
       <c r="O5" s="5">
         <v>550</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7283401058271604</v>
+        <v>0.7127121344550674</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4019104994035934</v>
+        <v>0.3595983597974263</v>
       </c>
       <c r="R5" s="5">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S5" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06758711403143478</v>
+        <v>0.06391484473433628</v>
       </c>
       <c r="O3" s="5">
         <v>863</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1070681769080011</v>
+        <v>0.1070902825328268</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09375849520376456</v>
+        <v>0.09372266686547262</v>
       </c>
       <c r="R3" s="5">
         <v>863</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5288203692683235</v>
+        <v>0.5326159710056331</v>
       </c>
       <c r="O4" s="5">
         <v>825</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1820652230963759</v>
+        <v>0.1820659370491772</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1575525373591131</v>
+        <v>0.1575165043239048</v>
       </c>
       <c r="R4" s="5">
         <v>825</v>
@@ -2275,16 +2275,16 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04447902433617364</v>
+        <v>0.03582684817150206</v>
       </c>
       <c r="O5" s="5">
         <v>740</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2777432615016237</v>
+        <v>0.2611632127829631</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1765125731106132</v>
+        <v>0.1567509029282786</v>
       </c>
       <c r="R5" s="5">
         <v>733</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09461727144166959</v>
+        <v>-0.08912574901751213</v>
       </c>
       <c r="O3" s="5">
         <v>874</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2151007541900198</v>
+        <v>0.2153281437875934</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1987831788120364</v>
+        <v>0.1987371975015834</v>
       </c>
       <c r="R3" s="5">
         <v>874</v>
@@ -2516,16 +2516,16 @@
         <v>21</v>
       </c>
       <c r="N4" s="4">
-        <v>1.013791610127357</v>
+        <v>0.6774671002563082</v>
       </c>
       <c r="O4" s="5">
         <v>684</v>
       </c>
       <c r="P4" s="4">
-        <v>3.799907251233735</v>
+        <v>3.784030361881833</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4048345501024522</v>
+        <v>0.2986248647518581</v>
       </c>
       <c r="R4" s="5">
         <v>664</v>
@@ -2575,22 +2575,22 @@
         <v>34</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9292749066123122</v>
+        <v>0.07646265750736347</v>
       </c>
       <c r="O5" s="5">
         <v>604</v>
       </c>
       <c r="P5" s="4">
-        <v>3.178314805562774</v>
+        <v>2.881157085132974</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8574251799673623</v>
+        <v>0.261336835876603</v>
       </c>
       <c r="R5" s="5">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="S5" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.002275395919727423</v>
+        <v>0.003864530805003596</v>
       </c>
       <c r="O3" s="5">
         <v>902</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0912091126130779</v>
+        <v>0.09121385940047234</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08412537067882105</v>
+        <v>0.08411086933533615</v>
       </c>
       <c r="R3" s="5">
         <v>902</v>
@@ -2816,22 +2816,22 @@
         <v>112</v>
       </c>
       <c r="N4" s="4">
-        <v>2.080453739519645</v>
+        <v>0.6864566326257773</v>
       </c>
       <c r="O4" s="5">
         <v>773</v>
       </c>
       <c r="P4" s="4">
-        <v>2.871590120617022</v>
+        <v>2.1679284959472</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.410890037703731</v>
+        <v>0.1399944082200012</v>
       </c>
       <c r="R4" s="5">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="S4" s="5">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2875,22 +2875,22 @@
         <v>94</v>
       </c>
       <c r="N5" s="4">
-        <v>1.32523703366444</v>
+        <v>0.006423902734240983</v>
       </c>
       <c r="O5" s="5">
         <v>659</v>
       </c>
       <c r="P5" s="4">
-        <v>2.701321121786875</v>
+        <v>2.014512027082149</v>
       </c>
       <c r="Q5" s="4">
-        <v>1.350496407292254</v>
+        <v>0.1213385858724559</v>
       </c>
       <c r="R5" s="5">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="S5" s="5">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1485042415266403</v>
+        <v>-0.1518853318357287</v>
       </c>
       <c r="O3" s="5">
         <v>912</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0859936900615717</v>
+        <v>0.08592723669272113</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08169180333727909</v>
+        <v>0.0816353789929839</v>
       </c>
       <c r="R3" s="5">
         <v>912</v>
@@ -3116,16 +3116,16 @@
         <v>14</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7205613532272972</v>
+        <v>0.5608419904237962</v>
       </c>
       <c r="O4" s="5">
         <v>681</v>
       </c>
       <c r="P4" s="4">
-        <v>2.676841877700531</v>
+        <v>2.654329847035218</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1857500547599551</v>
+        <v>0.1168850210615551</v>
       </c>
       <c r="R4" s="5">
         <v>667</v>
@@ -3175,16 +3175,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>0.077136963486872</v>
+        <v>-0.1834676199578098</v>
       </c>
       <c r="O5" s="5">
         <v>606</v>
       </c>
       <c r="P5" s="4">
-        <v>1.800543682063408</v>
+        <v>1.725769802539979</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2718783695871222</v>
+        <v>0.111992245396461</v>
       </c>
       <c r="R5" s="5">
         <v>592</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1176525444832861</v>
+        <v>0.1264718741076649</v>
       </c>
       <c r="O3" s="5">
         <v>887</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08168149122507344</v>
+        <v>0.08115377302531633</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05375479000831144</v>
+        <v>0.05300441643033803</v>
       </c>
       <c r="R3" s="5">
         <v>887</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3042899452663385</v>
+        <v>-0.2932596776663559</v>
       </c>
       <c r="O4" s="5">
         <v>847</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1508198978401864</v>
+        <v>0.1507029997005126</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1045944061445474</v>
+        <v>0.104176113386205</v>
       </c>
       <c r="R4" s="5">
         <v>847</v>
@@ -3475,16 +3475,16 @@
         <v>16</v>
       </c>
       <c r="N5" s="4">
-        <v>0.04839494755280598</v>
+        <v>0.1250223437255047</v>
       </c>
       <c r="O5" s="5">
         <v>750</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2325846200411077</v>
+        <v>0.2140334009264247</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1089498809115319</v>
+        <v>0.08396978151730565</v>
       </c>
       <c r="R5" s="5">
         <v>734</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1545227498594684</v>
+        <v>-0.1407000459766934</v>
       </c>
       <c r="O3" s="5">
         <v>916</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05840847492469877</v>
+        <v>0.05633076429505413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05565388151630912</v>
+        <v>0.05350594934891947</v>
       </c>
       <c r="R3" s="5">
         <v>916</v>
@@ -3716,16 +3716,16 @@
         <v>15</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06357013484805947</v>
+        <v>-0.1487901580767357</v>
       </c>
       <c r="O4" s="5">
         <v>851</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2472712154168003</v>
+        <v>0.2206887113088101</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1159985150874442</v>
+        <v>0.08563291161295181</v>
       </c>
       <c r="R4" s="5">
         <v>836</v>
@@ -3775,16 +3775,16 @@
         <v>36</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3008409244280677</v>
+        <v>-0.3928054411153319</v>
       </c>
       <c r="O5" s="5">
         <v>759</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3708021725290634</v>
+        <v>0.3408171006454039</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1121574624877428</v>
+        <v>0.07768611547345931</v>
       </c>
       <c r="R5" s="5">
         <v>722</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1184093683526064</v>
+        <v>0.1308387403005464</v>
       </c>
       <c r="O3" s="5">
         <v>887</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08744806846074012</v>
+        <v>0.08662078134661569</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06096582809511136</v>
+        <v>0.05981643739666229</v>
       </c>
       <c r="R3" s="5">
         <v>887</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1647925511081258</v>
+        <v>0.1807047515067097</v>
       </c>
       <c r="O4" s="5">
         <v>849</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1499922163048936</v>
+        <v>0.149352369783408</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1097595923524725</v>
+        <v>0.1087161349346532</v>
       </c>
       <c r="R4" s="5">
         <v>849</v>
@@ -4075,16 +4075,16 @@
         <v>16</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0740795643652709</v>
+        <v>0.1448187072928691</v>
       </c>
       <c r="O5" s="5">
         <v>744</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2399371899440081</v>
+        <v>0.227426330957145</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1032569483352546</v>
+        <v>0.08428534025551759</v>
       </c>
       <c r="R5" s="5">
         <v>728</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02725744240390541</v>
+        <v>-0.02472165172365948</v>
       </c>
       <c r="O3" s="5">
         <v>911</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06610130235708273</v>
+        <v>0.06607552875599029</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06146928905572296</v>
+        <v>0.06142079459507022</v>
       </c>
       <c r="R3" s="5">
         <v>911</v>
@@ -4316,22 +4316,22 @@
         <v>36</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5504812285231078</v>
+        <v>0.01516088818607386</v>
       </c>
       <c r="O4" s="5">
         <v>759</v>
       </c>
       <c r="P4" s="4">
-        <v>1.81912977691015</v>
+        <v>1.571480901248874</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5475778540501073</v>
+        <v>0.1560697713158139</v>
       </c>
       <c r="R4" s="5">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="S4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -4375,16 +4375,16 @@
         <v>33</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4316319560934572</v>
+        <v>-0.1147621056552346</v>
       </c>
       <c r="O5" s="5">
         <v>667</v>
       </c>
       <c r="P5" s="4">
-        <v>1.62390255172819</v>
+        <v>1.366863113548165</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5573806862063017</v>
+        <v>0.1537424667505171</v>
       </c>
       <c r="R5" s="5">
         <v>634</v>
@@ -4521,13 +4521,13 @@
         <v>1.636225266362253</v>
       </c>
       <c r="H3" s="4">
-        <v>1.603839398119619</v>
+        <v>1.570380141415235</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2503887752842477</v>
+        <v>0.1738998457870957</v>
       </c>
       <c r="J3" s="4">
-        <v>2.460112327675686</v>
+        <v>2.447410665269545</v>
       </c>
       <c r="K3" s="4">
         <v>85.1932485322896</v>
@@ -4571,13 +4571,13 @@
         <v>0.684931506849315</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3729118252549304</v>
+        <v>0.3703771990548365</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3080361107466925</v>
+        <v>0.3052688648751573</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3790126744400553</v>
+        <v>0.3805173488212104</v>
       </c>
       <c r="K4" s="4">
         <v>81.84100580871623</v>
@@ -4603,13 +4603,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>89.15525114155251</v>
+        <v>88.58447488584474</v>
       </c>
       <c r="C5" s="3">
         <v>2.777777777777778</v>
       </c>
       <c r="D5" s="3">
-        <v>8.06697108066971</v>
+        <v>8.637747336377473</v>
       </c>
       <c r="E5" s="3">
         <v>1.36986301369863</v>
@@ -4618,16 +4618,16 @@
         <v>3.006088280060883</v>
       </c>
       <c r="G5" s="3">
-        <v>3.691019786910198</v>
+        <v>4.26179604261796</v>
       </c>
       <c r="H5" s="4">
-        <v>0.8869655227861335</v>
+        <v>0.7437813700135029</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3572363640778014</v>
+        <v>0.1490043552807545</v>
       </c>
       <c r="J5" s="4">
-        <v>1.368039205131769</v>
+        <v>1.244933821992914</v>
       </c>
       <c r="K5" s="4">
         <v>91.19033381998136</v>
@@ -4653,13 +4653,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>83.67579908675799</v>
+        <v>83.29528158295282</v>
       </c>
       <c r="C6" s="3">
         <v>8.181126331811264</v>
       </c>
       <c r="D6" s="3">
-        <v>8.143074581430746</v>
+        <v>8.52359208523592</v>
       </c>
       <c r="E6" s="3">
         <v>1.06544901065449</v>
@@ -4668,16 +4668,16 @@
         <v>4.794520547945205</v>
       </c>
       <c r="G6" s="3">
-        <v>2.28310502283105</v>
+        <v>2.663622526636225</v>
       </c>
       <c r="H6" s="4">
-        <v>0.6259276687395378</v>
+        <v>0.5975964861841845</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3137198006770681</v>
+        <v>0.2542091695958678</v>
       </c>
       <c r="J6" s="4">
-        <v>0.8256905300766807</v>
+        <v>0.8233796654456426</v>
       </c>
       <c r="K6" s="4">
         <v>82.97303243976449</v>
@@ -4721,13 +4721,13 @@
         <v>3.729071537290715</v>
       </c>
       <c r="H7" s="4">
-        <v>1.925092631974459</v>
+        <v>1.715791064716045</v>
       </c>
       <c r="I7" s="4">
-        <v>0.4152786041209838</v>
+        <v>0.06994071716058758</v>
       </c>
       <c r="J7" s="4">
-        <v>2.506180676103521</v>
+        <v>2.30726718224309</v>
       </c>
       <c r="K7" s="4">
         <v>91.44940929187509</v>
@@ -4753,13 +4753,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>83.0289193302892</v>
+        <v>82.87671232876713</v>
       </c>
       <c r="C8" s="3">
         <v>4.680365296803653</v>
       </c>
       <c r="D8" s="3">
-        <v>12.29071537290715</v>
+        <v>12.44292237442922</v>
       </c>
       <c r="E8" s="3">
         <v>1.560121765601218</v>
@@ -4768,16 +4768,16 @@
         <v>7.229832572298325</v>
       </c>
       <c r="G8" s="3">
-        <v>3.50076103500761</v>
+        <v>3.65296803652968</v>
       </c>
       <c r="H8" s="4">
-        <v>1.022242104555708</v>
+        <v>0.959941866643149</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2498225050975524</v>
+        <v>0.1302459304243615</v>
       </c>
       <c r="J8" s="4">
-        <v>1.558108618327527</v>
+        <v>1.51445923782565</v>
       </c>
       <c r="K8" s="4">
         <v>88.70869961378773</v>
@@ -4803,13 +4803,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>75.98934550989345</v>
+        <v>75.79908675799086</v>
       </c>
       <c r="C9" s="3">
         <v>12.13850837138508</v>
       </c>
       <c r="D9" s="3">
-        <v>11.87214611872146</v>
+        <v>12.06240487062405</v>
       </c>
       <c r="E9" s="3">
         <v>0.76103500761035</v>
@@ -4818,16 +4818,16 @@
         <v>7.686453576864535</v>
       </c>
       <c r="G9" s="3">
-        <v>3.424657534246575</v>
+        <v>3.614916286149163</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6400165041591689</v>
+        <v>0.617156099704221</v>
       </c>
       <c r="I9" s="4">
-        <v>0.364640460960513</v>
+        <v>0.299447326861645</v>
       </c>
       <c r="J9" s="4">
-        <v>0.7400597039316763</v>
+        <v>0.7556767799517426</v>
       </c>
       <c r="K9" s="4">
         <v>80.37694529866741</v>
@@ -4871,13 +4871,13 @@
         <v>0.2663622526636225</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1850277775921205</v>
+        <v>0.1799381467357229</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1405527223346537</v>
+        <v>0.1345444813789973</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1806834117579051</v>
+        <v>0.1726927653694533</v>
       </c>
       <c r="K10" s="4">
         <v>88.48489319624339</v>
@@ -4903,13 +4903,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>80.28919330289193</v>
+        <v>80.25114155251141</v>
       </c>
       <c r="C11" s="3">
         <v>5.32724505327245</v>
       </c>
       <c r="D11" s="3">
-        <v>14.38356164383562</v>
+        <v>14.42161339421613</v>
       </c>
       <c r="E11" s="3">
         <v>5.098934550989346</v>
@@ -4918,16 +4918,16 @@
         <v>7.30593607305936</v>
       </c>
       <c r="G11" s="3">
-        <v>1.97869101978691</v>
+        <v>2.016742770167427</v>
       </c>
       <c r="H11" s="4">
-        <v>2.344289930510119</v>
+        <v>2.247611578097039</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4421771765360566</v>
+        <v>0.247134449548202</v>
       </c>
       <c r="J11" s="4">
-        <v>3.110305103910154</v>
+        <v>3.041657501243095</v>
       </c>
       <c r="K11" s="4">
         <v>85.45979198376453</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>81.46879756468797</v>
+        <v>80.97412480974124</v>
       </c>
       <c r="C12" s="3">
         <v>5.93607305936073</v>
       </c>
       <c r="D12" s="3">
-        <v>12.5951293759513</v>
+        <v>13.08980213089802</v>
       </c>
       <c r="E12" s="3">
         <v>2.43531202435312</v>
@@ -4968,16 +4968,16 @@
         <v>2.815829528158295</v>
       </c>
       <c r="G12" s="3">
-        <v>7.343987823439877</v>
+        <v>7.838660578386605</v>
       </c>
       <c r="H12" s="4">
-        <v>1.838488695398447</v>
+        <v>1.388219601380314</v>
       </c>
       <c r="I12" s="4">
-        <v>0.8358756961060667</v>
+        <v>0.1113536696390186</v>
       </c>
       <c r="J12" s="4">
-        <v>2.125875047597869</v>
+        <v>1.695478875133292</v>
       </c>
       <c r="K12" s="4">
         <v>89.91816285113737</v>
@@ -5021,13 +5021,13 @@
         <v>1.06544901065449</v>
       </c>
       <c r="H13" s="4">
-        <v>1.49352178180399</v>
+        <v>1.462858866921197</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1655228954233371</v>
+        <v>0.1007430603244419</v>
       </c>
       <c r="J13" s="4">
-        <v>2.305471194077953</v>
+        <v>2.289060927146529</v>
       </c>
       <c r="K13" s="4">
         <v>88.72610764244811</v>
@@ -5071,13 +5071,13 @@
         <v>0.60882800608828</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1515712648897049</v>
+        <v>0.1456416720987737</v>
       </c>
       <c r="I14" s="4">
-        <v>0.08761797946955768</v>
+        <v>0.07977548826804207</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1251559532766653</v>
+        <v>0.1162443263743348</v>
       </c>
       <c r="K14" s="4">
         <v>87.85992555317405</v>
@@ -5121,13 +5121,13 @@
         <v>1.97869101978691</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2186324227647951</v>
+        <v>0.1996475856247218</v>
       </c>
       <c r="I15" s="4">
-        <v>0.09253492400897043</v>
+        <v>0.07141873043002246</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3241583307291821</v>
+        <v>0.3084494461719705</v>
       </c>
       <c r="K15" s="4">
         <v>95.73600368610154</v>
@@ -5171,13 +5171,13 @@
         <v>0.60882800608828</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1555847253037042</v>
+        <v>0.1512289215899046</v>
       </c>
       <c r="I16" s="4">
-        <v>0.09027339359402527</v>
+        <v>0.08389484831021789</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1272706127858137</v>
+        <v>0.1194679839781412</v>
       </c>
       <c r="K16" s="4">
         <v>88.05642272129553</v>
@@ -5203,13 +5203,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>86.37747336377474</v>
+        <v>86.3013698630137</v>
       </c>
       <c r="C17" s="3">
         <v>3.691019786910198</v>
       </c>
       <c r="D17" s="3">
-        <v>9.931506849315069</v>
+        <v>10.0076103500761</v>
       </c>
       <c r="E17" s="3">
         <v>3.50076103500761</v>
@@ -5218,16 +5218,16 @@
         <v>3.881278538812785</v>
       </c>
       <c r="G17" s="3">
-        <v>2.549467275494673</v>
+        <v>2.625570776255707</v>
       </c>
       <c r="H17" s="4">
-        <v>1.140742792946026</v>
+        <v>0.9775532175490731</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3552298773440029</v>
+        <v>0.117401019601971</v>
       </c>
       <c r="J17" s="4">
-        <v>1.996634691105638</v>
+        <v>1.855998717436995</v>
       </c>
       <c r="K17" s="4">
         <v>91.66644663953859</v>
@@ -6198,13 +6198,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>2343</v>
+        <v>2328</v>
       </c>
       <c r="C5" s="5">
         <v>73</v>
       </c>
       <c r="D5" s="5">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E5" s="5">
         <v>36</v>
@@ -6213,7 +6213,7 @@
         <v>79</v>
       </c>
       <c r="G5" s="5">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="H5" s="5">
         <v>36</v>
@@ -6242,13 +6242,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>2199</v>
+        <v>2189</v>
       </c>
       <c r="C6" s="5">
         <v>215</v>
       </c>
       <c r="D6" s="5">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E6" s="5">
         <v>28</v>
@@ -6257,7 +6257,7 @@
         <v>126</v>
       </c>
       <c r="G6" s="5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5">
         <v>28</v>
@@ -6330,13 +6330,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="C8" s="5">
         <v>123</v>
       </c>
       <c r="D8" s="5">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E8" s="5">
         <v>41</v>
@@ -6345,7 +6345,7 @@
         <v>190</v>
       </c>
       <c r="G8" s="5">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H8" s="5">
         <v>41</v>
@@ -6374,13 +6374,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="C9" s="5">
         <v>319</v>
       </c>
       <c r="D9" s="5">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E9" s="5">
         <v>20</v>
@@ -6389,7 +6389,7 @@
         <v>202</v>
       </c>
       <c r="G9" s="5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H9" s="5">
         <v>20</v>
@@ -6462,13 +6462,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C11" s="5">
         <v>140</v>
       </c>
       <c r="D11" s="5">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E11" s="5">
         <v>134</v>
@@ -6477,7 +6477,7 @@
         <v>192</v>
       </c>
       <c r="G11" s="5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H11" s="5">
         <v>134</v>
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>2141</v>
+        <v>2128</v>
       </c>
       <c r="C12" s="5">
         <v>156</v>
       </c>
       <c r="D12" s="5">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="E12" s="5">
         <v>64</v>
@@ -6521,7 +6521,7 @@
         <v>74</v>
       </c>
       <c r="G12" s="5">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="H12" s="5">
         <v>64</v>
@@ -6726,13 +6726,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C17" s="5">
         <v>97</v>
       </c>
       <c r="D17" s="5">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E17" s="5">
         <v>92</v>
@@ -6741,7 +6741,7 @@
         <v>102</v>
       </c>
       <c r="G17" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H17" s="5">
         <v>92</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07952600696503768</v>
+        <v>-0.08263790664204862</v>
       </c>
       <c r="O3" s="5">
         <v>902</v>
       </c>
       <c r="P3" s="4">
-        <v>0.127594317313434</v>
+        <v>0.1274856544510622</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1197876135305364</v>
+        <v>0.1197483889405126</v>
       </c>
       <c r="R3" s="5">
         <v>902</v>
@@ -6983,16 +6983,16 @@
         <v>20</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6940438841340045</v>
+        <v>0.498393211120856</v>
       </c>
       <c r="O4" s="5">
         <v>682</v>
       </c>
       <c r="P4" s="4">
-        <v>2.595194324235674</v>
+        <v>2.594494033635464</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2929372889088343</v>
+        <v>0.2429121498085089</v>
       </c>
       <c r="R4" s="5">
         <v>662</v>
@@ -7042,16 +7042,16 @@
         <v>23</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4807830131816727</v>
+        <v>0.08709197228927223</v>
       </c>
       <c r="O5" s="5">
         <v>580</v>
       </c>
       <c r="P5" s="4">
-        <v>2.201858260601917</v>
+        <v>2.093931482582467</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4113136081071763</v>
+        <v>0.1795703463498288</v>
       </c>
       <c r="R5" s="5">
         <v>557</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1418326304085579</v>
+        <v>-0.1144404631704674</v>
       </c>
       <c r="O3" s="5">
         <v>818</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2116049344070962</v>
+        <v>0.2099520676202802</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2066701186441467</v>
+        <v>0.2052993056822798</v>
       </c>
       <c r="R3" s="5">
         <v>818</v>
@@ -7283,16 +7283,16 @@
         <v>14</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5441005212699151</v>
+        <v>0.4458276023215149</v>
       </c>
       <c r="O4" s="5">
         <v>770</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4778455021642342</v>
+        <v>0.4721126721674659</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4313050510100551</v>
+        <v>0.425048530525124</v>
       </c>
       <c r="R4" s="5">
         <v>767</v>
@@ -7342,16 +7342,16 @@
         <v>15</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2899082436118227</v>
+        <v>0.2897520276892465</v>
       </c>
       <c r="O5" s="5">
         <v>569</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4420030558687104</v>
+        <v>0.4419914556764398</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2870435193349296</v>
+        <v>0.2870452112041272</v>
       </c>
       <c r="R5" s="5">
         <v>554</v>
@@ -7524,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01665483512680748</v>
+        <v>-0.01644762598698435</v>
       </c>
       <c r="O3" s="5">
         <v>906</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0874347811056862</v>
+        <v>0.08743693420979438</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08143020088285033</v>
+        <v>0.08142943069376708</v>
       </c>
       <c r="R3" s="5">
         <v>906</v>
@@ -7583,22 +7583,22 @@
         <v>76</v>
       </c>
       <c r="N4" s="4">
-        <v>1.293570856884371</v>
+        <v>0.5426721083422308</v>
       </c>
       <c r="O4" s="5">
         <v>791</v>
       </c>
       <c r="P4" s="4">
-        <v>1.975888766367197</v>
+        <v>1.627182890673548</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7726321898742268</v>
+        <v>0.2109452044122176</v>
       </c>
       <c r="R4" s="5">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="S4" s="5">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7642,22 +7642,22 @@
         <v>44</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1360325530645945</v>
+        <v>-0.07426859917904949</v>
       </c>
       <c r="O5" s="5">
         <v>743</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6007731230582685</v>
+        <v>0.5204567834301084</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2754353162140007</v>
+        <v>0.1723020306149082</v>
       </c>
       <c r="R5" s="5">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S5" s="5">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -7824,16 +7824,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1367307879189856</v>
+        <v>-0.1441291445389652</v>
       </c>
       <c r="O3" s="5">
         <v>880</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1709549019958447</v>
+        <v>0.1707180316623776</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1620522584643504</v>
+        <v>0.16194565990005</v>
       </c>
       <c r="R3" s="5">
         <v>880</v>
@@ -7883,22 +7883,22 @@
         <v>62</v>
       </c>
       <c r="N4" s="4">
-        <v>1.283885810032353</v>
+        <v>0.8904624545029947</v>
       </c>
       <c r="O4" s="5">
         <v>743</v>
       </c>
       <c r="P4" s="4">
-        <v>1.143460215702502</v>
+        <v>1.067217933611422</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5043890735198354</v>
+        <v>0.348717818701791</v>
       </c>
       <c r="R4" s="5">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="S4" s="5">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -7942,22 +7942,22 @@
         <v>26</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2010141678128688</v>
+        <v>0.08526686773438996</v>
       </c>
       <c r="O5" s="5">
         <v>636</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5759316171720582</v>
+        <v>0.5683197223094213</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3134095690984464</v>
+        <v>0.279127093419739</v>
       </c>
       <c r="R5" s="5">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="S5" s="5">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8124,16 +8124,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02264211352126358</v>
+        <v>0.02479095247690566</v>
       </c>
       <c r="O3" s="5">
         <v>916</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0523291474879299</v>
+        <v>0.05230599647870583</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04705361015301595</v>
+        <v>0.04701375987109432</v>
       </c>
       <c r="R3" s="5">
         <v>916</v>
@@ -8183,16 +8183,16 @@
         <v>46</v>
       </c>
       <c r="N4" s="4">
-        <v>1.069910084373121</v>
+        <v>0.5042543234449113</v>
       </c>
       <c r="O4" s="5">
         <v>736</v>
       </c>
       <c r="P4" s="4">
-        <v>2.990761237546193</v>
+        <v>2.741317256982992</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5648908010719612</v>
+        <v>0.1015787760957775</v>
       </c>
       <c r="R4" s="5">
         <v>692</v>
@@ -8242,16 +8242,16 @@
         <v>54</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7856910444720416</v>
+        <v>-0.02196266653481871</v>
       </c>
       <c r="O5" s="5">
         <v>652</v>
       </c>
       <c r="P5" s="4">
-        <v>2.895896697993588</v>
+        <v>2.490860085213113</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8061857181420243</v>
+        <v>0.06844833604691607</v>
       </c>
       <c r="R5" s="5">
         <v>598</v>
